--- a/Documents/Product Catalog/10 Bedroom Set.xlsx
+++ b/Documents/Product Catalog/10 Bedroom Set.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9EB849-AB45-43E8-9BB9-3F60BC8E8C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10 Bed Room Set" sheetId="3" r:id="rId1"/>
@@ -17,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'10 Bed Room Set'!$A$1:$P$67</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1243,7 +1257,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="9">
     <font>
       <sz val="10"/>
@@ -1476,7 +1490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1553,28 +1567,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1586,22 +1579,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1801,7 +1794,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -1810,7 +1803,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1849,7 +1842,7 @@
         <xdr:cNvPr id="326" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1899,7 +1892,7 @@
         <xdr:cNvPr id="369" name="image28.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1949,7 +1942,7 @@
         <xdr:cNvPr id="370" name="image33.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1999,7 +1992,7 @@
         <xdr:cNvPr id="371" name="image28.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2049,7 +2042,7 @@
         <xdr:cNvPr id="372" name="image27.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2099,7 +2092,7 @@
         <xdr:cNvPr id="373" name="image32.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2149,7 +2142,7 @@
         <xdr:cNvPr id="374" name="image34.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2199,7 +2192,7 @@
         <xdr:cNvPr id="375" name="image35.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2249,7 +2242,7 @@
         <xdr:cNvPr id="376" name="image26.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2299,7 +2292,7 @@
         <xdr:cNvPr id="377" name="image30.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2349,7 +2342,7 @@
         <xdr:cNvPr id="378" name="image29.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2399,7 +2392,7 @@
         <xdr:cNvPr id="379" name="image31.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2449,7 +2442,7 @@
         <xdr:cNvPr id="380" name="image13.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2499,7 +2492,7 @@
         <xdr:cNvPr id="381" name="image25.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2549,7 +2542,7 @@
         <xdr:cNvPr id="382" name="image7.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2599,7 +2592,7 @@
         <xdr:cNvPr id="383" name="image4.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2649,7 +2642,7 @@
         <xdr:cNvPr id="384" name="image4.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2699,7 +2692,7 @@
         <xdr:cNvPr id="391" name="image3.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2749,7 +2742,7 @@
         <xdr:cNvPr id="392" name="image5.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2799,7 +2792,7 @@
         <xdr:cNvPr id="393" name="image8.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2849,7 +2842,7 @@
         <xdr:cNvPr id="394" name="image9.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2899,7 +2892,7 @@
         <xdr:cNvPr id="395" name="image5.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2949,7 +2942,7 @@
         <xdr:cNvPr id="396" name="image3.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2999,7 +2992,7 @@
         <xdr:cNvPr id="397" name="image22.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3049,7 +3042,7 @@
         <xdr:cNvPr id="398" name="Group 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3068,7 +3061,7 @@
           <xdr:cNvPr id="399" name="image23.jpeg">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3103,7 +3096,7 @@
           <xdr:cNvPr id="400" name="image24.jpeg">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3154,7 +3147,7 @@
         <xdr:cNvPr id="385" name="image85.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3204,7 +3197,7 @@
         <xdr:cNvPr id="386" name="image87.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3254,7 +3247,7 @@
         <xdr:cNvPr id="387" name="image88.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3304,7 +3297,7 @@
         <xdr:cNvPr id="388" name="image89.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3354,7 +3347,7 @@
         <xdr:cNvPr id="389" name="image90.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3404,7 +3397,7 @@
         <xdr:cNvPr id="390" name="image75.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3454,7 +3447,7 @@
         <xdr:cNvPr id="401" name="image76.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3504,7 +3497,7 @@
         <xdr:cNvPr id="402" name="image78.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3554,7 +3547,7 @@
         <xdr:cNvPr id="403" name="image98.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3604,7 +3597,7 @@
         <xdr:cNvPr id="404" name="image102.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3654,7 +3647,7 @@
         <xdr:cNvPr id="405" name="image103.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3699,7 +3692,7 @@
         <xdr:cNvPr id="406" name="image103.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3749,7 +3742,7 @@
         <xdr:cNvPr id="407" name="image116.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3799,7 +3792,7 @@
         <xdr:cNvPr id="408" name="image117.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3849,7 +3842,7 @@
         <xdr:cNvPr id="409" name="image118.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000085000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000085000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3899,7 +3892,7 @@
         <xdr:cNvPr id="410" name="image118.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000087000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000087000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3949,7 +3942,7 @@
         <xdr:cNvPr id="411" name="image123.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3999,7 +3992,7 @@
         <xdr:cNvPr id="412" name="image124.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4049,7 +4042,7 @@
         <xdr:cNvPr id="413" name="image125.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4099,7 +4092,7 @@
         <xdr:cNvPr id="414" name="image126.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4149,7 +4142,7 @@
         <xdr:cNvPr id="415" name="image127.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4199,7 +4192,7 @@
         <xdr:cNvPr id="416" name="image128.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000090000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000090000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4249,7 +4242,7 @@
         <xdr:cNvPr id="417" name="image130.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4299,7 +4292,7 @@
         <xdr:cNvPr id="418" name="image131.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000093000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000093000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4349,7 +4342,7 @@
         <xdr:cNvPr id="419" name="image133.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000095000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000095000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4399,7 +4392,7 @@
         <xdr:cNvPr id="420" name="image137.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000099000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000099000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4449,7 +4442,7 @@
         <xdr:cNvPr id="421" name="image138.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4499,7 +4492,7 @@
         <xdr:cNvPr id="422" name="image139.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4549,7 +4542,7 @@
         <xdr:cNvPr id="423" name="image143.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4599,7 +4592,7 @@
         <xdr:cNvPr id="424" name="image144.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A0000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4649,7 +4642,7 @@
         <xdr:cNvPr id="425" name="image149.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A9000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A9000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4699,7 +4692,7 @@
         <xdr:cNvPr id="426" name="image155.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AF000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AF000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4749,7 +4742,7 @@
         <xdr:cNvPr id="427" name="image153.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AD000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AD000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4799,7 +4792,7 @@
         <xdr:cNvPr id="428" name="image173.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C0000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4849,7 +4842,7 @@
         <xdr:cNvPr id="429" name="image174.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C1000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C1000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4899,7 +4892,7 @@
         <xdr:cNvPr id="430" name="image175.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C2000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C2000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4949,7 +4942,7 @@
         <xdr:cNvPr id="431" name="image100.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000071000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4999,7 +4992,7 @@
         <xdr:cNvPr id="432" name="image64.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00004C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5049,7 +5042,7 @@
         <xdr:cNvPr id="433" name="image160.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-0000B4000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B4000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5333,7 +5326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AS133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
@@ -5358,86 +5351,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
     </row>
     <row r="2" spans="1:45" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
     </row>
     <row r="3" spans="1:45" ht="50.1" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37" t="s">
+      <c r="G3" s="32"/>
+      <c r="H3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="37"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="37" t="s">
+      <c r="K3" s="32"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="N3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="37" t="s">
+      <c r="O3" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="P3" s="37" t="s">
+      <c r="P3" s="32" t="s">
         <v>187</v>
       </c>
       <c r="R3" s="4"/>
@@ -5470,19 +5463,19 @@
       <c r="AS3" s="4"/>
     </row>
     <row r="4" spans="1:45" ht="33.200000000000003" customHeight="1">
-      <c r="A4" s="40"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="34" t="s">
+      <c r="A4" s="31"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="37"/>
-      <c r="I4" s="42"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="34"/>
       <c r="J4" s="5" t="s">
         <v>15</v>
       </c>
@@ -5492,10 +5485,10 @@
       <c r="L4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -5559,7 +5552,7 @@
         <v>14500</v>
       </c>
       <c r="L5" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M5" s="23" t="s">
         <v>201</v>
@@ -5636,7 +5629,7 @@
         <v>16050</v>
       </c>
       <c r="L6" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M6" s="23" t="s">
         <v>201</v>
@@ -5713,7 +5706,7 @@
         <v>3900</v>
       </c>
       <c r="L7" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M7" s="23" t="s">
         <v>200</v>
@@ -5790,7 +5783,7 @@
         <v>19300</v>
       </c>
       <c r="L8" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M8" s="23" t="s">
         <v>216</v>
@@ -5867,7 +5860,7 @@
         <v>3990</v>
       </c>
       <c r="L9" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>200</v>
@@ -5944,7 +5937,7 @@
         <v>15900</v>
       </c>
       <c r="L10" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="23" t="s">
         <v>218</v>
@@ -6021,7 +6014,7 @@
         <v>4990</v>
       </c>
       <c r="L11" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M11" s="23" t="s">
         <v>219</v>
@@ -6098,7 +6091,7 @@
         <v>14500</v>
       </c>
       <c r="L12" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M12" s="23" t="s">
         <v>220</v>
@@ -6175,7 +6168,7 @@
         <v>5250</v>
       </c>
       <c r="L13" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>221</v>
@@ -6252,7 +6245,7 @@
         <v>15500</v>
       </c>
       <c r="L14" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M14" s="23" t="s">
         <v>222</v>
@@ -6329,7 +6322,7 @@
         <v>5500</v>
       </c>
       <c r="L15" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M15" s="23" t="s">
         <v>224</v>
@@ -6406,7 +6399,7 @@
         <v>15500</v>
       </c>
       <c r="L16" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M16" s="23" t="s">
         <v>225</v>
@@ -6483,7 +6476,7 @@
         <v>5590</v>
       </c>
       <c r="L17" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M17" s="23" t="s">
         <v>226</v>
@@ -6560,7 +6553,7 @@
         <v>22000</v>
       </c>
       <c r="L18" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M18" s="23" t="s">
         <v>227</v>
@@ -6637,7 +6630,7 @@
         <v>5900</v>
       </c>
       <c r="L19" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M19" s="23" t="s">
         <v>230</v>
@@ -6714,7 +6707,7 @@
         <v>15600</v>
       </c>
       <c r="L20" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M20" s="23" t="s">
         <v>188</v>
@@ -6791,7 +6784,7 @@
         <v>18500</v>
       </c>
       <c r="L21" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M21" s="23" t="s">
         <v>191</v>
@@ -6868,7 +6861,7 @@
         <v>4800</v>
       </c>
       <c r="L22" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M22" s="23" t="s">
         <v>192</v>
@@ -6945,7 +6938,7 @@
         <v>13000</v>
       </c>
       <c r="L23" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>195</v>
@@ -7022,7 +7015,7 @@
         <v>17800</v>
       </c>
       <c r="L24" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M24" s="23" t="s">
         <v>196</v>
@@ -7099,7 +7092,7 @@
         <v>2900</v>
       </c>
       <c r="L25" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M25" s="23" t="s">
         <v>194</v>
@@ -7176,7 +7169,7 @@
         <v>14980</v>
       </c>
       <c r="L26" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M26" s="23" t="s">
         <v>198</v>
@@ -7253,7 +7246,7 @@
         <v>18500</v>
       </c>
       <c r="L27" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M27" s="23" t="s">
         <v>199</v>
@@ -7330,7 +7323,7 @@
         <v>4400</v>
       </c>
       <c r="L28" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M28" s="23" t="s">
         <v>192</v>
@@ -7407,7 +7400,7 @@
         <v>10900</v>
       </c>
       <c r="L29" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M29" s="23" t="s">
         <v>238</v>
@@ -7484,7 +7477,7 @@
         <v>10990</v>
       </c>
       <c r="L30" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M30" s="23" t="s">
         <v>241</v>
@@ -7561,7 +7554,7 @@
         <v>11990</v>
       </c>
       <c r="L31" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M31" s="23" t="s">
         <v>242</v>
@@ -7638,7 +7631,7 @@
         <v>12990</v>
       </c>
       <c r="L32" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M32" s="23" t="s">
         <v>243</v>
@@ -7715,7 +7708,7 @@
         <v>11500</v>
       </c>
       <c r="L33" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M33" s="23" t="s">
         <v>244</v>
@@ -7792,7 +7785,7 @@
         <v>14990</v>
       </c>
       <c r="L34" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M34" s="23" t="s">
         <v>245</v>
@@ -7841,7 +7834,7 @@
         <v>11990</v>
       </c>
       <c r="L35" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M35" s="23" t="s">
         <v>237</v>
@@ -7890,7 +7883,7 @@
         <v>12990</v>
       </c>
       <c r="L36" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M36" s="23" t="s">
         <v>235</v>
@@ -7967,7 +7960,7 @@
         <v>13500</v>
       </c>
       <c r="L37" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M37" s="23" t="s">
         <v>235</v>
@@ -8044,7 +8037,7 @@
         <v>9980</v>
       </c>
       <c r="L38" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M38" s="23" t="s">
         <v>236</v>
@@ -8121,7 +8114,7 @@
         <v>17900</v>
       </c>
       <c r="L39" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M39" s="23" t="s">
         <v>250</v>
@@ -8198,7 +8191,7 @@
         <v>23000</v>
       </c>
       <c r="L40" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M40" s="23" t="s">
         <v>251</v>
@@ -8275,7 +8268,7 @@
         <v>22500</v>
       </c>
       <c r="L41" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M41" s="23" t="s">
         <v>251</v>
@@ -8352,7 +8345,7 @@
         <v>24500</v>
       </c>
       <c r="L42" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M42" s="23" t="s">
         <v>251</v>
@@ -8429,7 +8422,7 @@
         <v>18990</v>
       </c>
       <c r="L43" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M43" s="23" t="s">
         <v>252</v>
@@ -8506,7 +8499,7 @@
         <v>15900</v>
       </c>
       <c r="L44" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M44" s="23" t="s">
         <v>253</v>
@@ -8583,7 +8576,7 @@
         <v>22500</v>
       </c>
       <c r="L45" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M45" s="23" t="s">
         <v>254</v>
@@ -8660,7 +8653,7 @@
         <v>24500</v>
       </c>
       <c r="L46" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M46" s="23" t="s">
         <v>254</v>
@@ -8707,37 +8700,37 @@
       <c r="A47" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="B47" s="26" t="s">
+      <c r="B47" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="28" t="s">
+      <c r="D47" s="8"/>
+      <c r="E47" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="F47" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="30" t="s">
+      <c r="G47" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="H47" s="26" t="s">
+      <c r="H47" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="I47" s="26" t="s">
+      <c r="I47" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J47" s="28">
+      <c r="J47" s="9">
         <f t="shared" si="0"/>
         <v>12909</v>
       </c>
-      <c r="K47" s="31">
+      <c r="K47" s="18">
         <v>16550</v>
       </c>
-      <c r="L47" s="32">
-        <v>0.22</v>
+      <c r="L47" s="16">
+        <v>0.1</v>
       </c>
       <c r="M47" s="23" t="s">
         <v>255</v>
@@ -8814,7 +8807,7 @@
         <v>24990</v>
       </c>
       <c r="L48" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M48" s="23" t="s">
         <v>256</v>
@@ -8891,7 +8884,7 @@
         <v>16610</v>
       </c>
       <c r="L49" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M49" s="23" t="s">
         <v>257</v>
@@ -8968,7 +8961,7 @@
         <v>17110</v>
       </c>
       <c r="L50" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M50" s="23" t="s">
         <v>258</v>
@@ -9045,7 +9038,7 @@
         <v>16550</v>
       </c>
       <c r="L51" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M51" s="23" t="s">
         <v>259</v>
@@ -9122,7 +9115,7 @@
         <v>24800</v>
       </c>
       <c r="L52" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M52" s="23" t="s">
         <v>260</v>
@@ -9199,7 +9192,7 @@
         <v>16800</v>
       </c>
       <c r="L53" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M53" s="23" t="s">
         <v>261</v>
@@ -9276,7 +9269,7 @@
         <v>24990</v>
       </c>
       <c r="L54" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M54" s="23" t="s">
         <v>262</v>
@@ -9353,7 +9346,7 @@
         <v>16550</v>
       </c>
       <c r="L55" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M55" s="23" t="s">
         <v>263</v>
@@ -9430,7 +9423,7 @@
         <v>19990</v>
       </c>
       <c r="L56" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M56" s="23" t="s">
         <v>264</v>
@@ -9507,7 +9500,7 @@
         <v>15500</v>
       </c>
       <c r="L57" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M57" s="23" t="s">
         <v>267</v>
@@ -9584,7 +9577,7 @@
         <v>16100</v>
       </c>
       <c r="L58" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M58" s="23" t="s">
         <v>270</v>
@@ -9661,7 +9654,7 @@
         <v>15900</v>
       </c>
       <c r="L59" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M59" s="23" t="s">
         <v>271</v>
@@ -9738,7 +9731,7 @@
         <v>20400</v>
       </c>
       <c r="L60" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M60" s="23" t="s">
         <v>272</v>
@@ -9815,7 +9808,7 @@
         <v>15900</v>
       </c>
       <c r="L61" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M61" s="23" t="s">
         <v>273</v>
@@ -9892,7 +9885,7 @@
         <v>15990</v>
       </c>
       <c r="L62" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M62" s="23" t="s">
         <v>274</v>
@@ -9969,7 +9962,7 @@
         <v>14200</v>
       </c>
       <c r="L63" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M63" s="23" t="s">
         <v>278</v>
@@ -10018,7 +10011,7 @@
         <v>19990</v>
       </c>
       <c r="L64" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M64" s="23" t="s">
         <v>275</v>
@@ -10067,7 +10060,7 @@
         <v>17500</v>
       </c>
       <c r="L65" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M65" s="23" t="s">
         <v>284</v>
@@ -10144,7 +10137,7 @@
         <v>16400</v>
       </c>
       <c r="L66" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M66" s="23" t="s">
         <v>279</v>
@@ -10221,7 +10214,7 @@
         <v>13990</v>
       </c>
       <c r="L67" s="16">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="M67" s="23" t="s">
         <v>285</v>
@@ -10265,8 +10258,8 @@
       <c r="AS67" s="4"/>
     </row>
     <row r="68" spans="1:45" s="4" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A68" s="33"/>
-      <c r="B68" s="33"/>
+      <c r="A68" s="26"/>
+      <c r="B68" s="26"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>

--- a/Documents/Product Catalog/10 Bedroom Set.xlsx
+++ b/Documents/Product Catalog/10 Bedroom Set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9EB849-AB45-43E8-9BB9-3F60BC8E8C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6DC7E8-385C-443E-A1A2-FC1B9B3551AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Documents/Product Catalog/10 Bedroom Set.xlsx
+++ b/Documents/Product Catalog/10 Bedroom Set.xlsx
@@ -4298,7 +4298,7 @@
         <v/>
       </c>
       <c r="L30" s="15" t="n">
-        <v>10990</v>
+        <v>9990</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>0.1</v>
